--- a/1º Entrega/Tabla GEO.xlsx
+++ b/1º Entrega/Tabla GEO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\verit\Documents\MASTER BIOINFORMATICA\2º Cuatri\Trabajo Fin de Máster\TFM\04-26 Primera entrega\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\verit\Documents\MASTER BIOINFORMATICA\2º Cuatri\Trabajo Fin de Máster\TFM git\1º Entrega\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AFCAC0-7830-4DD7-92F9-71234BC910A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE46F55-B64A-460E-8927-AD256E9506F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39360" yWindow="3435" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>ID Dataset</t>
   </si>
@@ -54,27 +54,18 @@
     <t>Bulk RNA-seq</t>
   </si>
   <si>
-    <t>Raw Counts (indicado como RNA-seq counts), archivo .tar (GSE156451_RAW.tar)</t>
-  </si>
-  <si>
     <t>GSE50760</t>
   </si>
   <si>
     <t>54 muestras: 18 Colon normal, 18 CRC primario y 18 Metástasis hepática. Pareadas (de 18 pacientes).</t>
   </si>
   <si>
-    <t>Raw Counts (indicado como RNA-seq counts), archivo .tar (GSE50760_RAW.tar)</t>
-  </si>
-  <si>
     <t>GSE104836</t>
   </si>
   <si>
     <t>20 muestras: 10 tumores y 10 normales (pareadas).</t>
   </si>
   <si>
-    <t>Raw Counts (Conteos crudos disponibles en archivos suplementarios).</t>
-  </si>
-  <si>
     <t>hg38 (GRCh38)</t>
   </si>
   <si>
@@ -84,9 +75,6 @@
     <t>40 muestras: 20 tumores colorrectales y 20 tejidos normales emparejados.</t>
   </si>
   <si>
-    <t>GSE180440</t>
-  </si>
-  <si>
     <t>Gene expression profiling study by RNA-seq in colorectal cancer</t>
   </si>
   <si>
@@ -102,12 +90,6 @@
     <t>RNA-seq data of 20 pairs of colorectal tumor with matched adjacent normal colorectal tissue</t>
   </si>
   <si>
-    <t>NTRK1 fusions for the therapeutic intervention of Korean patients with colon cancer</t>
-  </si>
-  <si>
-    <t>200 muestras: 150 tumores y 50 controles normales pareadas.</t>
-  </si>
-  <si>
     <t>GSE92914</t>
   </si>
   <si>
@@ -127,6 +109,30 @@
   </si>
   <si>
     <t>524 muestras.</t>
+  </si>
+  <si>
+    <t>Identification of genes associated with the onset of colorectal cancer by transcriptomic analyses of the adenoma-carcinoma sequence</t>
+  </si>
+  <si>
+    <t>GSE164541</t>
+  </si>
+  <si>
+    <t>15 muestras: 5 tejido sano, 5 adenoma, 5 carcinoma; pareadas.</t>
+  </si>
+  <si>
+    <t>FPFM</t>
+  </si>
+  <si>
+    <t>Raw Counts (+ TPM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FPKM </t>
+  </si>
+  <si>
+    <t>RPKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raw Counts  + RPKM </t>
   </si>
 </sst>
 </file>
@@ -244,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -264,31 +270,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -486,6 +472,55 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -514,36 +549,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -558,15 +563,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD2B2E19-0CBD-4566-83F3-F74D8B8042D9}" name="Tabla1" displayName="Tabla1" ref="B2:G9" totalsRowShown="0" headerRowDxfId="7" dataDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
-  <autoFilter ref="B2:G9" xr:uid="{BD2B2E19-0CBD-4566-83F3-F74D8B8042D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD2B2E19-0CBD-4566-83F3-F74D8B8042D9}" name="Tabla1" displayName="Tabla1" ref="B2:G10" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="B2:G10" xr:uid="{BD2B2E19-0CBD-4566-83F3-F74D8B8042D9}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{56A8E861-EA05-4FA0-85D7-5F06F3B7F481}" name="ID Dataset" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{E099FF56-6989-4BE3-9E43-41C03E44173A}" name="Título del Estudio" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{2D5EAF6C-F494-4DAA-B00B-9C3CB37E6448}" name="Muestras (N)" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{70666772-DE6E-4961-92C3-67DC4D01627B}" name="Tecnología" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{2A8D16AF-4794-4AC1-A5FA-A3A66650314A}" name="Formato de Datos" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{E408799E-FB1F-4FD0-BFCE-057833096439}" name="Versión del Genoma" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{56A8E861-EA05-4FA0-85D7-5F06F3B7F481}" name="ID Dataset" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{E099FF56-6989-4BE3-9E43-41C03E44173A}" name="Título del Estudio" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{2D5EAF6C-F494-4DAA-B00B-9C3CB37E6448}" name="Muestras (N)" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{70666772-DE6E-4961-92C3-67DC4D01627B}" name="Tecnología" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{2A8D16AF-4794-4AC1-A5FA-A3A66650314A}" name="Formato de Datos" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{E408799E-FB1F-4FD0-BFCE-057833096439}" name="Versión del Genoma" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -835,18 +840,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:G10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" customWidth="1"/>
+    <col min="6" max="6" width="29.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,12 +871,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>7</v>
@@ -880,130 +885,138 @@
         <v>8</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="7" spans="2:7" s="7" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
+    <row r="9" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>16</v>
+      <c r="F10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
